--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$10</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="127">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-codeableconcept-timed-metadata</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-codeableconcept-timed-metadata</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -338,81 +338,56 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>Extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Extension.value[x].start</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
-    <t>closed</t>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>Extension.value[x]:valuePeriod</t>
-  </si>
-  <si>
-    <t>valuePeriod</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod.id</t>
-  </si>
-  <si>
-    <t>Extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod.extension</t>
-  </si>
-  <si>
-    <t>Extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod.start</t>
-  </si>
-  <si>
-    <t>Extension.value[x].start</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t>ele-1
-per-1</t>
-  </si>
-  <si>
     <t>./low</t>
-  </si>
-  <si>
-    <t>Extension.value[x]:valuePeriod.end</t>
   </si>
   <si>
     <t>Extension.value[x].end</t>
@@ -750,10 +725,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="27.703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1391,14 +1366,16 @@
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AC6" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>100</v>
@@ -1413,7 +1390,7 @@
         <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>99</v>
@@ -1421,14 +1398,12 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
@@ -1449,13 +1424,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1506,7 +1481,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -1515,32 +1490,32 @@
         <v>80</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1552,15 +1527,17 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>74</v>
@@ -1597,74 +1574,74 @@
         <v>74</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1702,42 +1679,42 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1751,16 +1728,16 @@
         <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>121</v>
@@ -1775,7 +1752,9 @@
       <c r="P10" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q10" s="2"/>
+      <c r="Q10" t="s" s="2">
+        <v>124</v>
+      </c>
       <c r="R10" t="s" s="2">
         <v>74</v>
       </c>
@@ -1819,7 +1798,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -1828,124 +1807,17 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>126</v>
       </c>
     </row>
-    <row r="11" hidden="true">
-      <c r="A11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q11" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="R11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK11">
+  <autoFilter ref="A1:AK10">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -1955,7 +1827,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI10">
+  <conditionalFormatting sqref="A2:AI9">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
